--- a/apps/web/public/templates/Student_Account_Import_Template.xlsx
+++ b/apps/web/public/templates/Student_Account_Import_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HK9\KLTN\KLTN_Project\execl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9210B350-E2CE-4FA9-9952-36F5438CA866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9C1379-CD89-4CCF-B5D0-8B582C575CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1005" yWindow="2880" windowWidth="15375" windowHeight="7785" xr2:uid="{1B6CC809-07B9-482A-8415-E567954F570C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1B6CC809-07B9-482A-8415-E567954F570C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Email</t>
   </si>
@@ -60,20 +60,79 @@
     <t>Địa chỉ liên lạc</t>
   </si>
   <si>
-    <t>Hình thức đào tạo</t>
-  </si>
-  <si>
-    <t>Trình độ đào tạo</t>
-  </si>
-  <si>
     <t>Niên khóa</t>
+  </si>
+  <si>
+    <t>Họ tên phụ huynh 1</t>
+  </si>
+  <si>
+    <t>Email phụ huynh 1</t>
+  </si>
+  <si>
+    <t>Số điện thoại phụ huynh 1</t>
+  </si>
+  <si>
+    <t>CCCD phụ huynh 1</t>
+  </si>
+  <si>
+    <t>Địa chỉ phụ huynh 1</t>
+  </si>
+  <si>
+    <t>Nghề nghiệp phụ huynh 1</t>
+  </si>
+  <si>
+    <t>Họ tên phụ huynh 2</t>
+  </si>
+  <si>
+    <t>Email phụ huynh 2</t>
+  </si>
+  <si>
+    <t>CCCD phụ huynh 2</t>
+  </si>
+  <si>
+    <t>Nghề nghiệp phụ huynh 2</t>
+  </si>
+  <si>
+    <t>Số điện thoại phụ huynh 2</t>
+  </si>
+  <si>
+    <t>Địa chỉ phụ huynh 2</t>
+  </si>
+  <si>
+    <t>Mối quan hệ với PH1
+1. Cha
+2. Mẹ
+3. Người giám hộ</t>
+  </si>
+  <si>
+    <t>Mối quan hệ với PH2
+1. Cha
+2. Mẹ
+3. Người giám hộ</t>
+  </si>
+  <si>
+    <t>Hình thức đào tạo
+1. Đại trà
+2. Chất lượng cao</t>
+  </si>
+  <si>
+    <t>Trình độ đào tạo
+1. Cử nhân
+2. Thạc sĩ
+3. Tiến sĩ</t>
+  </si>
+  <si>
+    <t>Dân tộc PH1</t>
+  </si>
+  <si>
+    <t>Dân tộc PH2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,8 +148,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -100,6 +173,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -128,16 +213,39 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -451,7 +559,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5307495-997D-415E-BDCE-EF03321AD104}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
@@ -460,74 +568,164 @@
     <col min="4" max="4" width="12.28515625" customWidth="1"/>
     <col min="5" max="5" width="10.42578125" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="9" max="9" width="11" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" customWidth="1"/>
     <col min="11" max="11" width="14.85546875" customWidth="1"/>
     <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19" customWidth="1"/>
+    <col min="19" max="19" width="19.42578125" customWidth="1"/>
+    <col min="21" max="21" width="25.42578125" customWidth="1"/>
+    <col min="22" max="22" width="20.5703125" customWidth="1"/>
+    <col min="23" max="23" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="24" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:30" s="8" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="5" t="s">
         <v>13</v>
       </c>
+      <c r="Q1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y1" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC1" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD1" s="9" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+    <row r="2" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
     </row>
+    <row r="3" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V1048576 AD2:AD1048576 M2:M1048576" xr:uid="{EB2FC39B-5A35-4758-9421-D3B2FD0C1D15}">
+      <formula1>"1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576" xr:uid="{E01A6D66-8935-4750-BDB9-F68542DFC7EF}">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>